--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3593,7 +3593,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>148</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3898,7 +3898,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>156</v>
       </c>
@@ -3913,13 +3913,13 @@
         <v>62</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -4001,7 +4001,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>159</v>
       </c>
@@ -4016,13 +4016,13 @@
         <v>160</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -4310,7 +4310,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>171</v>
       </c>
@@ -4325,13 +4325,13 @@
         <v>172</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4325,7 +4325,7 @@
         <v>172</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>75</v>
